--- a/education_forms/038_external_links_access_quiz--education_forms.xlsx
+++ b/education_forms/038_external_links_access_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1164,17 +1164,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>another_option</t>
+          <t>find_a_lock_icon_next_to_it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Another option</t>
+          <t>Find a lock icon next to it</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>find_a_lock_icon_next_to_it</t>
+          <t>find_the_https_in_the_address_bar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Find a lock icon next to it</t>
+          <t>Find the https in the address bar</t>
         </is>
       </c>
     </row>
@@ -1203,29 +1203,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>find_the_https_in_the_address_bar</t>
+          <t>another_option</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Find the https in the address bar</t>
+          <t>Another option</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quiz_question_1_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>another_option</t>
+          <t>a_non-secure_link_does_not_have_a_lock_icon_next_to_it</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Another option</t>
+          <t>A non-secure link does not have a lock icon next to it</t>
         </is>
       </c>
     </row>
@@ -1237,46 +1237,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a_non-secure_link_does_not_have_a_lock_icon_next_to_it</t>
+          <t>another_option</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A non-secure link does not have a lock icon next to it</t>
+          <t>Another option</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>another_option</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Another option</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>quiz_question_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>another_option</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Another option</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1288,53 +1288,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quiz_question_1_choices</t>
+          <t>quiz_question_1_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quiz_question_1_choices</t>
+          <t>quiz_question_1_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quiz_question_1_1_choices</t>
+          <t>quiz_question_1_1_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>quiz_question_1_1_choices</t>
+          <t>quiz_question_1_1_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>quiz_question_1_1_1_choices</t>
+          <t>quiz_question_1_1_1_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>quiz_question_1_1_1_choices</t>
+          <t>quiz_question_1_1_1_1_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quiz_question_1_1_1_1_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>quiz_question_1_1_1_1_choices</t>
+          <t>quiz_question_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1441,44 +1441,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>quiz_question_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>quiz_question_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
